--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="334">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,6 +791,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -881,8 +885,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Valeur de l'observation</t>
@@ -6717,7 +6721,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -6725,10 +6729,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6754,10 +6758,10 @@
         <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6788,7 +6792,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6806,7 +6810,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6826,10 +6830,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6927,10 +6931,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6971,7 +6975,7 @@
         <v>74</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>74</v>
@@ -7030,10 +7034,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7133,10 +7137,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7236,10 +7240,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7339,10 +7343,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7442,10 +7446,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7543,10 +7547,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7644,10 +7648,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7747,10 +7751,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7850,10 +7854,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7953,10 +7957,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7979,13 +7983,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8036,7 +8040,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8056,10 +8060,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8082,7 +8086,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8115,7 +8119,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8133,7 +8137,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8153,10 +8157,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8179,7 +8183,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8232,7 +8236,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8252,10 +8256,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8311,25 +8315,25 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8349,10 +8353,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8375,13 +8379,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8432,7 +8436,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8452,10 +8456,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8478,13 +8482,13 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8515,7 +8519,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8533,7 +8537,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8553,10 +8557,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8579,13 +8583,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8616,7 +8620,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8634,7 +8638,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8654,10 +8658,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8683,10 +8687,10 @@
         <v>161</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8737,7 +8741,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8757,10 +8761,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8783,7 +8787,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8836,7 +8840,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8856,10 +8860,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8882,7 +8886,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8935,7 +8939,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8955,10 +8959,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8981,7 +8985,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9034,7 +9038,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9054,10 +9058,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9080,13 +9084,13 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9137,7 +9141,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9157,10 +9161,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9183,7 +9187,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9236,7 +9240,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9256,10 +9260,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9282,7 +9286,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9335,7 +9339,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9355,10 +9359,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9381,7 +9385,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9434,7 +9438,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9454,10 +9458,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9480,7 +9484,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9533,7 +9537,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9553,10 +9557,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9579,7 +9583,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9632,7 +9636,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9652,10 +9656,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9678,7 +9682,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9731,7 +9735,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9751,10 +9755,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9777,11 +9781,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9832,7 +9836,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9852,10 +9856,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9953,10 +9957,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10054,10 +10058,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10155,10 +10159,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10256,10 +10260,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10359,10 +10363,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10462,10 +10466,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10565,10 +10569,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10668,10 +10672,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10769,10 +10773,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10806,7 +10810,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>74</v>
@@ -10828,7 +10832,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>74</v>
@@ -10846,7 +10850,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10866,10 +10870,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10892,7 +10896,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10945,7 +10949,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -10965,10 +10969,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10991,7 +10995,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11044,7 +11048,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
